--- a/teste.xlsx
+++ b/teste.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\teste_boletim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\teste_boletim2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04C5C85A-3CD6-496A-B7C6-EFD94D98866A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8CDDA9-8597-47EB-825B-8C7E57774436}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{74E8DE82-0940-46DC-A3ED-B463A51736DD}"/>
   </bookViews>
